--- a/PCB/电池子系统CMS模块/BOM.xlsx
+++ b/PCB/电池子系统CMS模块/BOM.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="158">
   <si>
     <t>参数</t>
   </si>
@@ -1127,6 +1127,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t>50</t>
     </r>
     <r>
@@ -1180,6 +1186,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>关键器件，对电流检测精度影响</t>
     </r>
     <r>
@@ -1279,6 +1291,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>关键器件，对温度和电压检测精度影响</t>
     </r>
     <r>
@@ -1385,17 +1403,11 @@
     <t>DR0012C</t>
   </si>
   <si>
-    <t>FM24C64D-DN-T-G</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>64Kbit(8K*8)I2C</t>
+    <t>FM24C512D-DN-T-G</t>
+  </si>
+  <si>
+    <r>
+      <t>512Kbit(64K*8)I2C</t>
     </r>
     <r>
       <rPr>
@@ -1422,7 +1434,27 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>，</t>
+      <t>，带有唯一ID和安全扇区</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> UDFN-8(2x3)</t>
+    </r>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>UDFN-8</t>
+  </si>
+  <si>
+    <r>
+      <t>程序内使用到了安全扇区和唯一UID，</t>
     </r>
     <r>
       <rPr>
@@ -1432,14 +1464,17 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
-UDFN-8(2x3)</t>
-    </r>
-  </si>
-  <si>
-    <t>U9</t>
-  </si>
-  <si>
-    <t>UDFN-8</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不能用其他型号代替否则程序起不来会报错！</t>
+    </r>
   </si>
   <si>
     <t>HT7533-3</t>
@@ -3852,7 +3887,7 @@
         <f t="shared" si="0"/>
         <v>1.95</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="9" t="s">
         <v>140</v>
       </c>
     </row>
@@ -3906,43 +3941,45 @@
       </c>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" ht="40.8" spans="1:8">
-      <c r="A47" s="14" t="s">
+    <row r="47" ht="55.2" spans="1:8">
+      <c r="A47" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="D47" s="14" t="s">
+      <c r="D47" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="6">
         <v>1</v>
       </c>
-      <c r="F47" s="2">
-        <v>1.703</v>
-      </c>
-      <c r="G47" s="2">
-        <f t="shared" si="0"/>
-        <v>1.703</v>
-      </c>
-      <c r="H47" s="2"/>
+      <c r="F47" s="6">
+        <v>1.23</v>
+      </c>
+      <c r="G47" s="6">
+        <f>E47*F47</f>
+        <v>1.23</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="48" ht="37.8" spans="1:8">
       <c r="A48" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E48" s="2">
         <v>1</v>
@@ -3958,7 +3995,7 @@
     </row>
     <row r="49" ht="17.4" spans="1:7">
       <c r="A49" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -3967,7 +4004,7 @@
       <c r="F49" s="11"/>
       <c r="G49" s="12">
         <f>SUM(G2:G48)</f>
-        <v>36.584</v>
+        <v>36.111</v>
       </c>
     </row>
     <row r="50" ht="39" customHeight="1"/>
